--- a/aq_files/0399.xlsx
+++ b/aq_files/0399.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,425 +413,578 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DATABASE SCHEMA</t>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Table: Employees</t>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>What are the key components of a useful data analysis report?</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>(emp_id INT, emp_name VARCHAR, age INT, salary INT, dept_id INT, joining_date DATE)</t>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>How do you identify the target audience for a data analysis report?</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>What types of KPIs or summary measures should be highlighted in a report?</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Table: Departments</t>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How would you choose the right visuals for a business report?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>(dept_id INT, dept_name VARCHAR)</t>
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Why are layout, readability, and consistency important in reporting?</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How can filters, drill-downs, or segmentation improve report usability?</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Assume tables are already created and populated.</t>
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What validation checks should be performed before publishing a report?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How would you present findings and recommendations clearly to stakeholders?</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SAMPLE DATA (for reference only)</t>
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What is • Creating Data Analysis reports as per the requirements?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Foundations</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>emp_id</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>emp_name</t>
+          <t>• Creating Data Analysis reports as per the requirements</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>Theory</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>Why is • Creating Data Analysis reports as per the requirements important in • Creating Data Analysis reports as per the requirements?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>dept_id</t>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>joining_date</t>
+          <t>Importance</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amit</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Explain the main workflow of • Creating Data Analysis reports as per the requirements.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>Process Understanding</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Neha</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>30</v>
-      </c>
-      <c r="D13" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>List the key components involved in • Creating Data Analysis reports as per the requirements.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>Component Awareness</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Raj</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>28</v>
-      </c>
-      <c r="D14" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How is • Creating Data Analysis reports as per the requirements applied in a practical business scenario?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>Applied Understanding</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Simran</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What problem does • Creating Data Analysis reports as per the requirements help solve?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>Problem Framing</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>26</v>
-      </c>
-      <c r="D16" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Describe the core steps required to complete • Creating Data Analysis reports as per the requirements.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>Execution Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>What inputs are typically required before starting • Creating Data Analysis reports as per the requirements?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Input Readiness</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Question No</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Write Query</t>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>What outputs or results are expected from • Creating Data Analysis reports as per the requirements?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Output Interpretation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Find all employee details.</t>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>How would you validate whether • Creating Data Analysis reports as per the requirements was completed correctly?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Validation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Retrieve only employee names and salaries.</t>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>What are common mistakes to avoid while working on • Creating Data Analysis reports as per the requirements?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Error Awareness</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Find employees earning more than 50000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Count total number of employees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>List distinct department IDs from Employees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Sort employees by salary in descending order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>7</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Find average salary of employees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>8</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Find employees who joined after 2021.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>9</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Find maximum salary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Find minimum age.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>11</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Find employees aged between 25 and 30.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>12</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Count employees in each department.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>13</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Find employees whose name starts with 'A'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>14</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Find employees in department 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>15</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Find total salary paid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Find employees ordered by joining_date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>17</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Find employees with salary between 40000 and 60000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>18</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Find top 3 highest paid employees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>19</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Find employees not in department 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>20</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Find employees whose age is greater than average age.</t>
+          <t>• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>How does • Creating Data Analysis reports as per the requirements improve decision-making or outcomes?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Course CDA | DAA-131/DATA ANALYSIS BUSINESS REPORTING/• Creating Data Analysis reports as per the requirements</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Business Value</t>
         </is>
       </c>
     </row>
